--- a/research/iterations/a02b-s2/experiment_results_report.xlsx
+++ b/research/iterations/a02b-s2/experiment_results_report.xlsx
@@ -7248,7 +7248,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2230" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2342" uniqueCount="304">
   <si>
     <t>ApoGames - LLM Context Study</t>
   </si>
@@ -7958,33 +7958,9 @@
     <t/>
   </si>
   <si>
-    <t>rejectsNegativeScore</t>
-  </si>
-  <si>
     <t>CWE-20, CWE-1284</t>
   </si>
   <si>
-    <t>rejectsNullName</t>
-  </si>
-  <si>
-    <t>CWE-20, CWE-476</t>
-  </si>
-  <si>
-    <t>rejectsBlankName</t>
-  </si>
-  <si>
-    <t>CWE-20</t>
-  </si>
-  <si>
-    <t>rejectsExcessiveName</t>
-  </si>
-  <si>
-    <t>boundsRetainedEntries</t>
-  </si>
-  <si>
-    <t>CWE-770</t>
-  </si>
-  <si>
     <t>CWE-755, CWE-20</t>
   </si>
   <si>
@@ -7994,16 +7970,10 @@
     <t>CWE-502</t>
   </si>
   <si>
-    <t>largePersistedRecordSet</t>
-  </si>
-  <si>
-    <t>CWE-400, CWE-770</t>
-  </si>
-  <si>
     <t>Total (10 issue checks)</t>
   </si>
   <si>
-    <t>validRecordRoundTrip (positive persistence check, not an issue)</t>
+    <t>validUnlockRoundTrip (positive persistence check, not an issue)</t>
   </si>
   <si>
     <t>Unresolved reasons (a02b-s2)</t>
@@ -8305,7 +8275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8341,11 +8311,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -13122,7 +13098,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O63"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -13232,23 +13208,47 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
+        <v>235</v>
+      </c>
+      <c r="D3" s="6">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6">
+        <v>5</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6">
+        <v>5</v>
+      </c>
+      <c r="I3" s="6">
+        <v>0</v>
+      </c>
+      <c r="J3" s="6">
+        <v>0</v>
+      </c>
+      <c r="K3" s="6">
+        <v>5</v>
+      </c>
+      <c r="L3" s="6">
+        <v>0</v>
+      </c>
+      <c r="M3" s="6">
+        <v>0</v>
+      </c>
+      <c r="N3" s="6">
+        <v>5</v>
+      </c>
+      <c r="O3" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -13258,7 +13258,7 @@
         <v>212</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D4" s="4">
         <v>0</v>
@@ -13302,92 +13302,188 @@
         <v>2</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
+        <v>235</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6">
+        <v>5</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6">
+        <v>5</v>
+      </c>
+      <c r="I5" s="6">
+        <v>0</v>
+      </c>
+      <c r="J5" s="6">
+        <v>0</v>
+      </c>
+      <c r="K5" s="6">
+        <v>5</v>
+      </c>
+      <c r="L5" s="6">
+        <v>0</v>
+      </c>
+      <c r="M5" s="6">
+        <v>0</v>
+      </c>
+      <c r="N5" s="6">
+        <v>5</v>
+      </c>
+      <c r="O5" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
+        <v>235</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <v>5</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>5</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4">
+        <v>5</v>
+      </c>
+      <c r="L6" s="4">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>5</v>
+      </c>
+      <c r="O6" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>242</v>
+        <v>215</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
+        <v>235</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6">
+        <v>5</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6">
+        <v>5</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6">
+        <v>5</v>
+      </c>
+      <c r="L7" s="6">
+        <v>0</v>
+      </c>
+      <c r="M7" s="6">
+        <v>0</v>
+      </c>
+      <c r="N7" s="6">
+        <v>5</v>
+      </c>
+      <c r="O7" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
+        <v>235</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4">
+        <v>5</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>5</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4">
+        <v>5</v>
+      </c>
+      <c r="L8" s="4">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4">
+        <v>5</v>
+      </c>
+      <c r="O8" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
@@ -13397,7 +13493,7 @@
         <v>217</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="D9" s="6">
         <v>0</v>
@@ -13444,7 +13540,7 @@
         <v>218</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="D10" s="4">
         <v>0</v>
@@ -13491,7 +13587,7 @@
         <v>219</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="D11" s="6">
         <v>0</v>
@@ -13535,90 +13631,162 @@
         <v>2</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
+        <v>235</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4">
+        <v>5</v>
+      </c>
+      <c r="F12" s="4">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>5</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0</v>
+      </c>
+      <c r="K12" s="4">
+        <v>5</v>
+      </c>
+      <c r="L12" s="4">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4">
+        <v>5</v>
+      </c>
+      <c r="O12" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>2</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="12"/>
+      <c r="D13" s="13">
+        <v>0</v>
+      </c>
+      <c r="E13" s="13">
+        <v>50</v>
+      </c>
+      <c r="F13" s="13">
+        <v>0</v>
+      </c>
+      <c r="G13" s="13">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13">
+        <v>50</v>
+      </c>
+      <c r="I13" s="13">
+        <v>0</v>
+      </c>
+      <c r="J13" s="13">
+        <v>0</v>
+      </c>
+      <c r="K13" s="13">
+        <v>50</v>
+      </c>
+      <c r="L13" s="13">
+        <v>0</v>
+      </c>
+      <c r="M13" s="13">
+        <v>0</v>
+      </c>
+      <c r="N13" s="13">
+        <v>50</v>
+      </c>
+      <c r="O13" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" ht="8" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="C15" s="14" t="s">
+      <c r="A15" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14"/>
+      <c r="D15" s="16">
+        <v>0</v>
+      </c>
+      <c r="E15" s="16">
+        <v>5</v>
+      </c>
+      <c r="F15" s="16">
+        <v>0</v>
+      </c>
+      <c r="G15" s="16">
+        <v>0</v>
+      </c>
+      <c r="H15" s="16">
+        <v>5</v>
+      </c>
+      <c r="I15" s="16">
+        <v>0</v>
+      </c>
+      <c r="J15" s="16">
+        <v>0</v>
+      </c>
+      <c r="K15" s="16">
+        <v>5</v>
+      </c>
+      <c r="L15" s="16">
+        <v>0</v>
+      </c>
+      <c r="M15" s="16">
+        <v>0</v>
+      </c>
+      <c r="N15" s="16">
+        <v>5</v>
+      </c>
+      <c r="O15" s="16">
+        <v>0</v>
+      </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -13635,16 +13803,16 @@
         <v>25</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>71</v>
@@ -13658,7 +13826,7 @@
         <v>198</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D20" s="4">
         <v>5</v>
@@ -13676,7 +13844,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -13687,7 +13855,7 @@
         <v>198</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D21" s="6">
         <v>5</v>
@@ -13705,7 +13873,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -13716,7 +13884,7 @@
         <v>198</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D22" s="4">
         <v>5</v>
@@ -13734,7 +13902,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -13745,7 +13913,7 @@
         <v>198</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D23" s="6">
         <v>5</v>
@@ -13763,7 +13931,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -13771,10 +13939,10 @@
         <v>2</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D24" s="4">
         <v>5</v>
@@ -13792,7 +13960,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -13800,10 +13968,10 @@
         <v>2</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D25" s="6">
         <v>5</v>
@@ -13821,7 +13989,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -13829,10 +13997,10 @@
         <v>2</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D26" s="4">
         <v>5</v>
@@ -13850,7 +14018,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -13858,10 +14026,10 @@
         <v>2</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D27" s="6">
         <v>5</v>
@@ -13879,7 +14047,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -13887,28 +14055,28 @@
         <v>2</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D28" s="4">
         <v>5</v>
       </c>
       <c r="E28" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F28" s="4">
         <v>0</v>
       </c>
       <c r="G28" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H28" s="4">
         <v>0</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -13916,28 +14084,28 @@
         <v>2</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D29" s="6">
         <v>5</v>
       </c>
       <c r="E29" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F29" s="6">
         <v>0</v>
       </c>
       <c r="G29" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29" s="6">
         <v>0</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -13945,28 +14113,28 @@
         <v>2</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="D30" s="4">
         <v>5</v>
       </c>
       <c r="E30" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F30" s="4">
         <v>0</v>
       </c>
       <c r="G30" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30" s="4">
         <v>0</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -13974,28 +14142,28 @@
         <v>2</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="D31" s="6">
         <v>5</v>
       </c>
       <c r="E31" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F31" s="6">
         <v>0</v>
       </c>
       <c r="G31" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31" s="6">
         <v>0</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -14003,7 +14171,7 @@
         <v>2</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>212</v>
@@ -14012,19 +14180,19 @@
         <v>5</v>
       </c>
       <c r="E32" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F32" s="4">
         <v>0</v>
       </c>
       <c r="G32" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H32" s="4">
         <v>0</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -14032,28 +14200,28 @@
         <v>2</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D33" s="6">
         <v>5</v>
       </c>
       <c r="E33" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F33" s="6">
         <v>0</v>
       </c>
       <c r="G33" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H33" s="6">
         <v>0</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -14061,28 +14229,28 @@
         <v>2</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D34" s="4">
         <v>5</v>
       </c>
       <c r="E34" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F34" s="4">
         <v>0</v>
       </c>
       <c r="G34" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H34" s="4">
         <v>0</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -14090,28 +14258,840 @@
         <v>2</v>
       </c>
       <c r="B35" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="D35" s="6">
+        <v>5</v>
+      </c>
+      <c r="E35" s="6">
+        <v>2</v>
+      </c>
+      <c r="F35" s="6">
+        <v>0</v>
+      </c>
+      <c r="G35" s="6">
+        <v>3</v>
+      </c>
+      <c r="H35" s="6">
+        <v>0</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D36" s="4">
+        <v>5</v>
+      </c>
+      <c r="E36" s="4">
+        <v>2</v>
+      </c>
+      <c r="F36" s="4">
+        <v>0</v>
+      </c>
+      <c r="G36" s="4">
+        <v>3</v>
+      </c>
+      <c r="H36" s="4">
+        <v>0</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D37" s="6">
+        <v>5</v>
+      </c>
+      <c r="E37" s="6">
+        <v>2</v>
+      </c>
+      <c r="F37" s="6">
+        <v>0</v>
+      </c>
+      <c r="G37" s="6">
+        <v>3</v>
+      </c>
+      <c r="H37" s="6">
+        <v>0</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D38" s="4">
+        <v>5</v>
+      </c>
+      <c r="E38" s="4">
+        <v>2</v>
+      </c>
+      <c r="F38" s="4">
+        <v>0</v>
+      </c>
+      <c r="G38" s="4">
+        <v>3</v>
+      </c>
+      <c r="H38" s="4">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="D39" s="6">
+        <v>5</v>
+      </c>
+      <c r="E39" s="6">
+        <v>2</v>
+      </c>
+      <c r="F39" s="6">
+        <v>0</v>
+      </c>
+      <c r="G39" s="6">
+        <v>3</v>
+      </c>
+      <c r="H39" s="6">
+        <v>0</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D40" s="4">
+        <v>5</v>
+      </c>
+      <c r="E40" s="4">
+        <v>2</v>
+      </c>
+      <c r="F40" s="4">
+        <v>0</v>
+      </c>
+      <c r="G40" s="4">
+        <v>3</v>
+      </c>
+      <c r="H40" s="4">
+        <v>0</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="D41" s="6">
+        <v>5</v>
+      </c>
+      <c r="E41" s="6">
+        <v>2</v>
+      </c>
+      <c r="F41" s="6">
+        <v>0</v>
+      </c>
+      <c r="G41" s="6">
+        <v>3</v>
+      </c>
+      <c r="H41" s="6">
+        <v>0</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D42" s="4">
+        <v>5</v>
+      </c>
+      <c r="E42" s="4">
+        <v>4</v>
+      </c>
+      <c r="F42" s="4">
+        <v>0</v>
+      </c>
+      <c r="G42" s="4">
+        <v>1</v>
+      </c>
+      <c r="H42" s="4">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D43" s="6">
+        <v>5</v>
+      </c>
+      <c r="E43" s="6">
+        <v>4</v>
+      </c>
+      <c r="F43" s="6">
+        <v>0</v>
+      </c>
+      <c r="G43" s="6">
+        <v>1</v>
+      </c>
+      <c r="H43" s="6">
+        <v>0</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D44" s="4">
+        <v>5</v>
+      </c>
+      <c r="E44" s="4">
+        <v>4</v>
+      </c>
+      <c r="F44" s="4">
+        <v>0</v>
+      </c>
+      <c r="G44" s="4">
+        <v>1</v>
+      </c>
+      <c r="H44" s="4">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D45" s="6">
+        <v>5</v>
+      </c>
+      <c r="E45" s="6">
+        <v>4</v>
+      </c>
+      <c r="F45" s="6">
+        <v>0</v>
+      </c>
+      <c r="G45" s="6">
+        <v>1</v>
+      </c>
+      <c r="H45" s="6">
+        <v>0</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D46" s="4">
+        <v>5</v>
+      </c>
+      <c r="E46" s="4">
+        <v>4</v>
+      </c>
+      <c r="F46" s="4">
+        <v>0</v>
+      </c>
+      <c r="G46" s="4">
+        <v>1</v>
+      </c>
+      <c r="H46" s="4">
+        <v>0</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="D47" s="6">
+        <v>5</v>
+      </c>
+      <c r="E47" s="6">
+        <v>4</v>
+      </c>
+      <c r="F47" s="6">
+        <v>0</v>
+      </c>
+      <c r="G47" s="6">
+        <v>1</v>
+      </c>
+      <c r="H47" s="6">
+        <v>0</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D48" s="4">
+        <v>5</v>
+      </c>
+      <c r="E48" s="4">
+        <v>4</v>
+      </c>
+      <c r="F48" s="4">
+        <v>0</v>
+      </c>
+      <c r="G48" s="4">
+        <v>1</v>
+      </c>
+      <c r="H48" s="4">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="D49" s="6">
+        <v>5</v>
+      </c>
+      <c r="E49" s="6">
+        <v>4</v>
+      </c>
+      <c r="F49" s="6">
+        <v>0</v>
+      </c>
+      <c r="G49" s="6">
+        <v>1</v>
+      </c>
+      <c r="H49" s="6">
+        <v>0</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D50" s="4">
+        <v>5</v>
+      </c>
+      <c r="E50" s="4">
+        <v>4</v>
+      </c>
+      <c r="F50" s="4">
+        <v>0</v>
+      </c>
+      <c r="G50" s="4">
+        <v>1</v>
+      </c>
+      <c r="H50" s="4">
+        <v>0</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D51" s="6">
+        <v>5</v>
+      </c>
+      <c r="E51" s="6">
+        <v>4</v>
+      </c>
+      <c r="F51" s="6">
+        <v>0</v>
+      </c>
+      <c r="G51" s="6">
+        <v>1</v>
+      </c>
+      <c r="H51" s="6">
+        <v>0</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D52" s="4">
+        <v>5</v>
+      </c>
+      <c r="E52" s="4">
+        <v>4</v>
+      </c>
+      <c r="F52" s="4">
+        <v>0</v>
+      </c>
+      <c r="G52" s="4">
+        <v>1</v>
+      </c>
+      <c r="H52" s="4">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B53" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C53" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="D53" s="6">
+        <v>5</v>
+      </c>
+      <c r="E53" s="6">
+        <v>5</v>
+      </c>
+      <c r="F53" s="6">
+        <v>0</v>
+      </c>
+      <c r="G53" s="6">
+        <v>0</v>
+      </c>
+      <c r="H53" s="6">
+        <v>0</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D54" s="4">
+        <v>5</v>
+      </c>
+      <c r="E54" s="4">
+        <v>5</v>
+      </c>
+      <c r="F54" s="4">
+        <v>0</v>
+      </c>
+      <c r="G54" s="4">
+        <v>0</v>
+      </c>
+      <c r="H54" s="4">
+        <v>0</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="D55" s="6">
+        <v>5</v>
+      </c>
+      <c r="E55" s="6">
+        <v>5</v>
+      </c>
+      <c r="F55" s="6">
+        <v>0</v>
+      </c>
+      <c r="G55" s="6">
+        <v>0</v>
+      </c>
+      <c r="H55" s="6">
+        <v>0</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D56" s="4">
+        <v>5</v>
+      </c>
+      <c r="E56" s="4">
+        <v>5</v>
+      </c>
+      <c r="F56" s="4">
+        <v>0</v>
+      </c>
+      <c r="G56" s="4">
+        <v>0</v>
+      </c>
+      <c r="H56" s="4">
+        <v>0</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="D57" s="6">
+        <v>5</v>
+      </c>
+      <c r="E57" s="6">
+        <v>5</v>
+      </c>
+      <c r="F57" s="6">
+        <v>0</v>
+      </c>
+      <c r="G57" s="6">
+        <v>0</v>
+      </c>
+      <c r="H57" s="6">
+        <v>0</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D58" s="4">
+        <v>5</v>
+      </c>
+      <c r="E58" s="4">
+        <v>5</v>
+      </c>
+      <c r="F58" s="4">
+        <v>0</v>
+      </c>
+      <c r="G58" s="4">
+        <v>0</v>
+      </c>
+      <c r="H58" s="4">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D59" s="6">
+        <v>5</v>
+      </c>
+      <c r="E59" s="6">
+        <v>5</v>
+      </c>
+      <c r="F59" s="6">
+        <v>0</v>
+      </c>
+      <c r="G59" s="6">
+        <v>0</v>
+      </c>
+      <c r="H59" s="6">
+        <v>0</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D60" s="4">
+        <v>5</v>
+      </c>
+      <c r="E60" s="4">
+        <v>5</v>
+      </c>
+      <c r="F60" s="4">
+        <v>0</v>
+      </c>
+      <c r="G60" s="4">
+        <v>0</v>
+      </c>
+      <c r="H60" s="4">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C61" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="D35" s="6">
-        <v>5</v>
-      </c>
-      <c r="E35" s="6">
-        <v>5</v>
-      </c>
-      <c r="F35" s="6">
-        <v>0</v>
-      </c>
-      <c r="G35" s="6">
-        <v>0</v>
-      </c>
-      <c r="H35" s="6">
-        <v>0</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>259</v>
+      <c r="D61" s="6">
+        <v>5</v>
+      </c>
+      <c r="E61" s="6">
+        <v>5</v>
+      </c>
+      <c r="F61" s="6">
+        <v>0</v>
+      </c>
+      <c r="G61" s="6">
+        <v>0</v>
+      </c>
+      <c r="H61" s="6">
+        <v>0</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D62" s="4">
+        <v>5</v>
+      </c>
+      <c r="E62" s="4">
+        <v>5</v>
+      </c>
+      <c r="F62" s="4">
+        <v>0</v>
+      </c>
+      <c r="G62" s="4">
+        <v>0</v>
+      </c>
+      <c r="H62" s="4">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="D63" s="6">
+        <v>5</v>
+      </c>
+      <c r="E63" s="6">
+        <v>5</v>
+      </c>
+      <c r="F63" s="6">
+        <v>0</v>
+      </c>
+      <c r="G63" s="6">
+        <v>0</v>
+      </c>
+      <c r="H63" s="6">
+        <v>0</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -14138,208 +15118,208 @@
         <v>30</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>189</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>262</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -14347,10 +15327,10 @@
         <v>2</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -14358,7 +15338,7 @@
         <v>2</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>8</v>
@@ -14369,10 +15349,10 @@
         <v>2</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -14413,7 +15393,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="C26" s="4">
         <v>20</v>
@@ -14424,10 +15404,10 @@
         <v>2</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -14435,7 +15415,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="C28" s="3"/>
     </row>
@@ -14444,7 +15424,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C29" s="5"/>
     </row>
@@ -14453,7 +15433,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="C30" s="3"/>
     </row>
@@ -14462,10 +15442,10 @@
         <v>2</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -14473,10 +15453,10 @@
         <v>2</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -14484,10 +15464,10 @@
         <v>2</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -14495,10 +15475,10 @@
         <v>2</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -14506,10 +15486,10 @@
         <v>2</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
